--- a/outputs/comparison/essentiality/GeneEssentiality.xlsx
+++ b/outputs/comparison/essentiality/GeneEssentiality.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>iYO844</t>
+          <t>iYO844_Minimal_iBsu1147</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -539,10 +539,10 @@
         <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G2" t="n">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="H2" t="n">
         <v>31</v>
@@ -551,147 +551,31 @@
         <v>0.6961000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8623</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5824</v>
+        <v>0.5896</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4572</v>
+        <v>0.4509</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4176</v>
+        <v>0.4104</v>
       </c>
       <c r="N2" t="n">
         <v>0.6961000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8623</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5221</v>
+        <v>0.5164</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.8458</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="R2" t="n">
         <v>0.1949</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>iBB1018</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1020</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4331</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1014</v>
-      </c>
-      <c r="E3" t="n">
-        <v>116</v>
-      </c>
-      <c r="F3" t="n">
-        <v>117</v>
-      </c>
-      <c r="G3" t="n">
-        <v>761</v>
-      </c>
-      <c r="H3" t="n">
-        <v>20</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.8529</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.5021</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.4979</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.8529</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.8667</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.6287</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.8649</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.2355</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>iBsu1147R</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1155</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4331</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1152</v>
-      </c>
-      <c r="E4" t="n">
-        <v>166</v>
-      </c>
-      <c r="F4" t="n">
-        <v>122</v>
-      </c>
-      <c r="G4" t="n">
-        <v>832</v>
-      </c>
-      <c r="H4" t="n">
-        <v>32</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8384</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.8721</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.4236</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.5764</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.8384</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.8721</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.6831</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.8663</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.2667</v>
       </c>
     </row>
   </sheetData>
